--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.61</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -610,6 +614,170 @@
       </c>
       <c r="T2" t="n">
         <v>32.93</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Trabzonspor x Hearts</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hearts</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>2915</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>200</v>
+      </c>
+      <c r="S3" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T3" t="n">
+        <v>32.93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Inter Club Escaldes x Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inter Club Escaldes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>29.84</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-22.xlsx
@@ -664,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.34</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -746,15 +750,19 @@
       <c r="K4" t="n">
         <v>1.54</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,88 @@
       </c>
       <c r="T4" t="n">
         <v>29.84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin x Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>3463</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T5" t="n">
+        <v>36.73</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-22.xlsx
@@ -836,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.3</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
